--- a/app/placed_bets.xlsx
+++ b/app/placed_bets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -554,6 +554,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -942,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T205"/>
+  <dimension ref="A1:T208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1019,12 +1028,12 @@
         </is>
       </c>
       <c r="K1" s="2" t="n"/>
-      <c r="L1" s="154" t="inlineStr">
+      <c r="L1" s="157" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="M1" s="155" t="inlineStr">
+      <c r="M1" s="158" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
@@ -1103,38 +1112,38 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J2" s="154" t="n">
+      <c r="J2" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73.53</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13060</v>
+        <v>13210</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12152.5</v>
+        <v>12270</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-907.5</v>
+        <v>-940</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
         <v>1.31</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>122.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -1175,7 +1184,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J3" s="155" t="n">
+      <c r="J3" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n"/>
@@ -1227,7 +1236,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J4" s="154" t="n">
+      <c r="J4" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -1279,7 +1288,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J5" s="154" t="n">
+      <c r="J5" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1331,7 +1340,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J6" s="154" t="n">
+      <c r="J6" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -1383,7 +1392,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J7" s="155" t="n">
+      <c r="J7" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -1435,7 +1444,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J8" s="154" t="n">
+      <c r="J8" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1487,7 +1496,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J9" s="155" t="n">
+      <c r="J9" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1539,7 +1548,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J10" s="154" t="n">
+      <c r="J10" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1591,7 +1600,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J11" s="154" t="n">
+      <c r="J11" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1643,7 +1652,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J12" s="155" t="n">
+      <c r="J12" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1695,7 +1704,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J13" s="154" t="n">
+      <c r="J13" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1747,7 +1756,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J14" s="154" t="n">
+      <c r="J14" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1799,7 +1808,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J15" s="154" t="n">
+      <c r="J15" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1851,7 +1860,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J16" s="154" t="n">
+      <c r="J16" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1903,7 +1912,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J17" s="155" t="n">
+      <c r="J17" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -1955,7 +1964,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J18" s="154" t="n">
+      <c r="J18" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -2007,7 +2016,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J19" s="155" t="n">
+      <c r="J19" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n"/>
@@ -2059,7 +2068,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J20" s="154" t="n">
+      <c r="J20" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -2111,7 +2120,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J21" s="155" t="n">
+      <c r="J21" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="2" t="n"/>
@@ -2163,7 +2172,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J22" s="154" t="n">
+      <c r="J22" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -2215,7 +2224,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J23" s="155" t="n">
+      <c r="J23" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n"/>
@@ -2267,7 +2276,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J24" s="154" t="n">
+      <c r="J24" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -2319,7 +2328,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J25" s="154" t="n">
+      <c r="J25" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -2371,7 +2380,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J26" s="154" t="n">
+      <c r="J26" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2423,7 +2432,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J27" s="154" t="n">
+      <c r="J27" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2475,7 +2484,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J28" s="154" t="n">
+      <c r="J28" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2527,7 +2536,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J29" s="155" t="n">
+      <c r="J29" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2579,7 +2588,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J30" s="154" t="n">
+      <c r="J30" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2631,7 +2640,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J31" s="154" t="n">
+      <c r="J31" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2683,7 +2692,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J32" s="154" t="n">
+      <c r="J32" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2735,7 +2744,7 @@
           <t>2 - 5</t>
         </is>
       </c>
-      <c r="J33" s="154" t="n">
+      <c r="J33" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2787,7 +2796,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J34" s="155" t="n">
+      <c r="J34" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="2" t="n"/>
@@ -2839,7 +2848,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J35" s="154" t="n">
+      <c r="J35" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2891,7 +2900,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J36" s="154" t="n">
+      <c r="J36" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2943,7 +2952,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J37" s="154" t="n">
+      <c r="J37" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -2995,7 +3004,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J38" s="154" t="n">
+      <c r="J38" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3047,7 +3056,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J39" s="154" t="n">
+      <c r="J39" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3099,7 +3108,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J40" s="154" t="n">
+      <c r="J40" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3151,7 +3160,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J41" s="154" t="n">
+      <c r="J41" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3203,7 +3212,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J42" s="154" t="n">
+      <c r="J42" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -3255,7 +3264,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J43" s="155" t="n">
+      <c r="J43" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="2" t="n"/>
@@ -3307,7 +3316,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J44" s="154" t="n">
+      <c r="J44" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3359,7 +3368,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J45" s="155" t="n">
+      <c r="J45" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="2" t="n"/>
@@ -3411,7 +3420,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J46" s="154" t="n">
+      <c r="J46" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -3463,7 +3472,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J47" s="154" t="n">
+      <c r="J47" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3515,7 +3524,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J48" s="155" t="n">
+      <c r="J48" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n"/>
@@ -3567,7 +3576,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J49" s="154" t="n">
+      <c r="J49" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3619,7 +3628,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J50" s="154" t="n">
+      <c r="J50" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3671,7 +3680,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J51" s="154" t="n">
+      <c r="J51" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3723,7 +3732,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J52" s="155" t="n">
+      <c r="J52" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="2" t="n"/>
@@ -3775,7 +3784,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J53" s="154" t="n">
+      <c r="J53" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="2" t="n"/>
@@ -3827,7 +3836,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J54" s="155" t="n">
+      <c r="J54" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="2" t="n"/>
@@ -3879,7 +3888,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J55" s="155" t="n">
+      <c r="J55" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="2" t="n"/>
@@ -3931,7 +3940,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J56" s="154" t="n">
+      <c r="J56" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -3983,7 +3992,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J57" s="154" t="n">
+      <c r="J57" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4035,7 +4044,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J58" s="154" t="n">
+      <c r="J58" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4087,7 +4096,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J59" s="155" t="n">
+      <c r="J59" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="2" t="n"/>
@@ -4139,7 +4148,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J60" s="155" t="n">
+      <c r="J60" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="2" t="n"/>
@@ -4191,7 +4200,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J61" s="155" t="n">
+      <c r="J61" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="2" t="n"/>
@@ -4243,7 +4252,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J62" s="154" t="n">
+      <c r="J62" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4295,7 +4304,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J63" s="154" t="n">
+      <c r="J63" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4347,7 +4356,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J64" s="154" t="n">
+      <c r="J64" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4399,7 +4408,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J65" s="154" t="n">
+      <c r="J65" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4451,7 +4460,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J66" s="155" t="n">
+      <c r="J66" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="2" t="n"/>
@@ -4503,7 +4512,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J67" s="154" t="n">
+      <c r="J67" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -4555,7 +4564,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J68" s="154" t="n">
+      <c r="J68" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4607,7 +4616,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J69" s="154" t="n">
+      <c r="J69" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4659,7 +4668,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J70" s="154" t="n">
+      <c r="J70" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4711,7 +4720,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J71" s="155" t="n">
+      <c r="J71" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="2" t="n"/>
@@ -4763,7 +4772,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J72" s="154" t="n">
+      <c r="J72" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -4815,7 +4824,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J73" s="154" t="n">
+      <c r="J73" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -4867,7 +4876,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J74" s="154" t="n">
+      <c r="J74" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -4919,7 +4928,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J75" s="154" t="n">
+      <c r="J75" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -4971,7 +4980,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J76" s="154" t="n">
+      <c r="J76" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5023,7 +5032,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J77" s="155" t="n">
+      <c r="J77" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K77" s="2" t="n"/>
@@ -5075,7 +5084,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J78" s="155" t="n">
+      <c r="J78" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n"/>
@@ -5127,7 +5136,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J79" s="154" t="n">
+      <c r="J79" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5179,7 +5188,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J80" s="155" t="n">
+      <c r="J80" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="2" t="n"/>
@@ -5231,7 +5240,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J81" s="154" t="n">
+      <c r="J81" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5283,7 +5292,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J82" s="154" t="n">
+      <c r="J82" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5335,7 +5344,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J83" s="155" t="n">
+      <c r="J83" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K83" s="2" t="n"/>
@@ -5387,7 +5396,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J84" s="155" t="n">
+      <c r="J84" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="2" t="n"/>
@@ -5439,7 +5448,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J85" s="154" t="n">
+      <c r="J85" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5491,7 +5500,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J86" s="154" t="n">
+      <c r="J86" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5543,7 +5552,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J87" s="154" t="n">
+      <c r="J87" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5595,7 +5604,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J88" s="154" t="n">
+      <c r="J88" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -5647,7 +5656,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J89" s="154" t="n">
+      <c r="J89" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -5699,7 +5708,7 @@
           <t>1 - 6</t>
         </is>
       </c>
-      <c r="J90" s="154" t="n">
+      <c r="J90" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -5751,7 +5760,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J91" s="154" t="n">
+      <c r="J91" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -5803,7 +5812,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J92" s="154" t="n">
+      <c r="J92" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -5855,7 +5864,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J93" s="154" t="n">
+      <c r="J93" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -5907,7 +5916,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J94" s="154" t="n">
+      <c r="J94" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -5959,7 +5968,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J95" s="154" t="n">
+      <c r="J95" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6011,7 +6020,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J96" s="154" t="n">
+      <c r="J96" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="n"/>
@@ -6063,7 +6072,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J97" s="154" t="n">
+      <c r="J97" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="2" t="n"/>
@@ -6115,7 +6124,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J98" s="154" t="n">
+      <c r="J98" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n"/>
@@ -6167,7 +6176,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J99" s="155" t="n">
+      <c r="J99" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K99" s="2" t="n"/>
@@ -6219,7 +6228,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J100" s="154" t="n">
+      <c r="J100" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="2" t="n"/>
@@ -6271,7 +6280,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J101" s="154" t="n">
+      <c r="J101" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n"/>
@@ -6323,7 +6332,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J102" s="154" t="n">
+      <c r="J102" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n"/>
@@ -6375,7 +6384,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J103" s="155" t="n">
+      <c r="J103" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="2" t="n"/>
@@ -6427,7 +6436,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J104" s="154" t="n">
+      <c r="J104" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n"/>
@@ -6479,7 +6488,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J105" s="154" t="n">
+      <c r="J105" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -6531,7 +6540,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J106" s="154" t="n">
+      <c r="J106" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -6583,7 +6592,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J107" s="154" t="n">
+      <c r="J107" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -6635,7 +6644,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J108" s="154" t="n">
+      <c r="J108" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6687,7 +6696,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J109" s="155" t="n">
+      <c r="J109" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="2" t="n"/>
@@ -6739,7 +6748,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J110" s="154" t="n">
+      <c r="J110" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6791,7 +6800,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J111" s="154" t="n">
+      <c r="J111" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6843,7 +6852,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J112" s="154" t="n">
+      <c r="J112" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="2" t="n"/>
@@ -6895,7 +6904,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J113" s="154" t="n">
+      <c r="J113" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n"/>
@@ -6947,7 +6956,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J114" s="154" t="n">
+      <c r="J114" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n"/>
@@ -6999,7 +7008,7 @@
           <t>4 - 3</t>
         </is>
       </c>
-      <c r="J115" s="154" t="n">
+      <c r="J115" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n"/>
@@ -7051,7 +7060,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J116" s="154" t="n">
+      <c r="J116" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -7103,7 +7112,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J117" s="154" t="n">
+      <c r="J117" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7155,7 +7164,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J118" s="154" t="n">
+      <c r="J118" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="2" t="n"/>
@@ -7207,7 +7216,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J119" s="155" t="n">
+      <c r="J119" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K119" s="2" t="n"/>
@@ -7259,7 +7268,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J120" s="154" t="n">
+      <c r="J120" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -7311,7 +7320,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J121" s="154" t="n">
+      <c r="J121" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="2" t="n"/>
@@ -7363,7 +7372,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J122" s="155" t="n">
+      <c r="J122" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K122" s="2" t="n"/>
@@ -7415,7 +7424,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J123" s="154" t="n">
+      <c r="J123" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="2" t="n"/>
@@ -7467,7 +7476,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J124" s="154" t="n">
+      <c r="J124" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="2" t="n"/>
@@ -7519,7 +7528,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J125" s="154" t="n">
+      <c r="J125" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="2" t="n"/>
@@ -7571,7 +7580,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J126" s="155" t="n">
+      <c r="J126" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K126" s="2" t="n"/>
@@ -7623,7 +7632,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J127" s="154" t="n">
+      <c r="J127" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="2" t="n"/>
@@ -7675,7 +7684,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J128" s="154" t="n">
+      <c r="J128" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="2" t="n"/>
@@ -7727,7 +7736,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J129" s="154" t="n">
+      <c r="J129" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="2" t="n"/>
@@ -7779,7 +7788,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J130" s="155" t="n">
+      <c r="J130" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K130" s="2" t="n"/>
@@ -7831,7 +7840,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J131" s="154" t="n">
+      <c r="J131" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="2" t="n"/>
@@ -7883,7 +7892,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J132" s="154" t="n">
+      <c r="J132" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="2" t="n"/>
@@ -7935,7 +7944,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J133" s="154" t="n">
+      <c r="J133" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="2" t="n"/>
@@ -7987,7 +7996,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J134" s="154" t="n">
+      <c r="J134" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="2" t="n"/>
@@ -8039,7 +8048,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J135" s="154" t="n">
+      <c r="J135" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="2" t="n"/>
@@ -8091,7 +8100,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J136" s="154" t="n">
+      <c r="J136" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="2" t="n"/>
@@ -8143,7 +8152,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J137" s="154" t="n">
+      <c r="J137" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="2" t="n"/>
@@ -8195,7 +8204,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J138" s="154" t="n">
+      <c r="J138" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -8247,7 +8256,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J139" s="154" t="n">
+      <c r="J139" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -8299,7 +8308,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J140" s="154" t="n">
+      <c r="J140" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="2" t="n"/>
@@ -8351,7 +8360,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J141" s="154" t="n">
+      <c r="J141" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="2" t="n"/>
@@ -8403,7 +8412,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J142" s="154" t="n">
+      <c r="J142" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="2" t="n"/>
@@ -8455,7 +8464,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J143" s="155" t="n">
+      <c r="J143" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K143" s="2" t="n"/>
@@ -8507,7 +8516,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J144" s="154" t="n">
+      <c r="J144" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -8559,7 +8568,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J145" s="155" t="n">
+      <c r="J145" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K145" s="2" t="n"/>
@@ -8611,7 +8620,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J146" s="154" t="n">
+      <c r="J146" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="2" t="n"/>
@@ -8663,7 +8672,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J147" s="154" t="n">
+      <c r="J147" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="2" t="n"/>
@@ -8715,7 +8724,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J148" s="154" t="n">
+      <c r="J148" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="2" t="n"/>
@@ -8767,7 +8776,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J149" s="155" t="n">
+      <c r="J149" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K149" s="2" t="n"/>
@@ -8819,7 +8828,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J150" s="154" t="n">
+      <c r="J150" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8871,7 +8880,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J151" s="154" t="n">
+      <c r="J151" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8923,7 +8932,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J152" s="154" t="n">
+      <c r="J152" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -8975,7 +8984,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J153" s="155" t="n">
+      <c r="J153" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="2" t="n"/>
@@ -9027,7 +9036,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J154" s="155" t="n">
+      <c r="J154" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K154" s="2" t="n"/>
@@ -9079,7 +9088,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J155" s="155" t="n">
+      <c r="J155" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K155" s="2" t="n"/>
@@ -9131,7 +9140,7 @@
           <t>3 - 4</t>
         </is>
       </c>
-      <c r="J156" s="155" t="n">
+      <c r="J156" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K156" s="2" t="n"/>
@@ -9183,7 +9192,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J157" s="154" t="n">
+      <c r="J157" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n"/>
@@ -9235,7 +9244,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J158" s="154" t="n">
+      <c r="J158" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="2" t="n"/>
@@ -9287,7 +9296,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J159" s="154" t="n">
+      <c r="J159" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="2" t="n"/>
@@ -9339,7 +9348,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J160" s="154" t="n">
+      <c r="J160" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="2" t="n"/>
@@ -9391,7 +9400,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J161" s="155" t="n">
+      <c r="J161" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="2" t="n"/>
@@ -9443,7 +9452,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J162" s="155" t="n">
+      <c r="J162" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="2" t="n"/>
@@ -9495,7 +9504,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J163" s="154" t="n">
+      <c r="J163" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -9547,7 +9556,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J164" s="154" t="n">
+      <c r="J164" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="2" t="n"/>
@@ -9599,7 +9608,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J165" s="154" t="n">
+      <c r="J165" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="2" t="n"/>
@@ -9651,7 +9660,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J166" s="155" t="n">
+      <c r="J166" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K166" s="2" t="n"/>
@@ -9703,7 +9712,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J167" s="154" t="n">
+      <c r="J167" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="2" t="n"/>
@@ -9755,7 +9764,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J168" s="155" t="n">
+      <c r="J168" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K168" s="2" t="n"/>
@@ -9807,7 +9816,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J169" s="154" t="n">
+      <c r="J169" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="2" t="n"/>
@@ -9859,7 +9868,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J170" s="154" t="n">
+      <c r="J170" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="2" t="n"/>
@@ -9911,7 +9920,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J171" s="154" t="n">
+      <c r="J171" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9963,7 +9972,7 @@
           <t>6 - 2</t>
         </is>
       </c>
-      <c r="J172" s="154" t="n">
+      <c r="J172" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="2" t="n"/>
@@ -10015,7 +10024,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J173" s="154" t="n">
+      <c r="J173" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="2" t="n"/>
@@ -10067,7 +10076,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J174" s="154" t="n">
+      <c r="J174" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="2" t="n"/>
@@ -10119,7 +10128,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J175" s="155" t="n">
+      <c r="J175" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K175" s="2" t="n"/>
@@ -10171,7 +10180,7 @@
           <t>6 - 1</t>
         </is>
       </c>
-      <c r="J176" s="154" t="n">
+      <c r="J176" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -10223,7 +10232,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J177" s="155" t="n">
+      <c r="J177" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K177" s="2" t="n"/>
@@ -10275,7 +10284,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J178" s="154" t="n">
+      <c r="J178" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="2" t="n"/>
@@ -10327,7 +10336,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J179" s="154" t="n">
+      <c r="J179" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="2" t="n"/>
@@ -10379,7 +10388,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J180" s="154" t="n">
+      <c r="J180" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="2" t="n"/>
@@ -10431,7 +10440,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J181" s="154" t="n">
+      <c r="J181" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n"/>
@@ -10483,7 +10492,7 @@
           <t>6 - 0</t>
         </is>
       </c>
-      <c r="J182" s="154" t="n">
+      <c r="J182" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n"/>
@@ -10535,7 +10544,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J183" s="155" t="n">
+      <c r="J183" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K183" s="2" t="n"/>
@@ -10587,7 +10596,7 @@
           <t>2 - 4</t>
         </is>
       </c>
-      <c r="J184" s="154" t="n">
+      <c r="J184" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="2" t="n"/>
@@ -10639,7 +10648,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J185" s="154" t="n">
+      <c r="J185" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="2" t="n"/>
@@ -10691,7 +10700,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J186" s="155" t="n">
+      <c r="J186" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K186" s="2" t="n"/>
@@ -10743,7 +10752,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J187" s="154" t="n">
+      <c r="J187" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="2" t="n"/>
@@ -10795,7 +10804,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J188" s="155" t="n">
+      <c r="J188" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K188" s="2" t="n"/>
@@ -10847,7 +10856,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J189" s="154" t="n">
+      <c r="J189" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="2" t="n"/>
@@ -10899,7 +10908,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J190" s="154" t="n">
+      <c r="J190" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="2" t="n"/>
@@ -10951,7 +10960,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J191" s="155" t="n">
+      <c r="J191" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K191" s="2" t="n"/>
@@ -11003,7 +11012,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J192" s="154" t="n">
+      <c r="J192" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="2" t="n"/>
@@ -11055,7 +11064,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J193" s="154" t="n">
+      <c r="J193" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K193" s="2" t="n"/>
@@ -11107,7 +11116,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J194" s="155" t="n">
+      <c r="J194" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K194" s="2" t="n"/>
@@ -11159,7 +11168,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J195" s="154" t="n">
+      <c r="J195" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K195" s="2" t="n"/>
@@ -11211,7 +11220,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J196" s="155" t="n">
+      <c r="J196" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="2" t="n"/>
@@ -11263,7 +11272,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J197" s="154" t="n">
+      <c r="J197" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K197" s="2" t="n"/>
@@ -11315,7 +11324,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J198" s="154" t="n">
+      <c r="J198" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -11367,7 +11376,7 @@
           <t>3 - 5</t>
         </is>
       </c>
-      <c r="J199" s="154" t="n">
+      <c r="J199" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K199" s="2" t="n"/>
@@ -11419,7 +11428,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J200" s="155" t="n">
+      <c r="J200" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K200" s="2" t="n"/>
@@ -11471,7 +11480,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J201" s="154" t="n">
+      <c r="J201" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K201" s="2" t="n"/>
@@ -11523,7 +11532,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J202" s="154" t="n">
+      <c r="J202" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K202" s="2" t="n"/>
@@ -11575,7 +11584,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J203" s="154" t="n">
+      <c r="J203" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K203" s="2" t="n"/>
@@ -11627,7 +11636,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J204" s="155" t="n">
+      <c r="J204" s="158" t="n">
         <v>0</v>
       </c>
       <c r="K204" s="2" t="n"/>
@@ -11679,7 +11688,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J205" s="154" t="n">
+      <c r="J205" s="157" t="n">
         <v>1</v>
       </c>
       <c r="K205" s="2" t="n"/>
@@ -11692,6 +11701,162 @@
       <c r="R205" s="2" t="n"/>
       <c r="S205" s="2" t="n"/>
       <c r="T205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>14.02.2026</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>St Pauli</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>56.49999999999999</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>6.499999999999993</v>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+      <c r="J206" s="157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="2" t="n"/>
+      <c r="L206" s="2" t="n"/>
+      <c r="M206" s="2" t="n"/>
+      <c r="N206" s="2" t="n"/>
+      <c r="O206" s="2" t="n"/>
+      <c r="P206" s="2" t="n"/>
+      <c r="Q206" s="2" t="n"/>
+      <c r="R206" s="2" t="n"/>
+      <c r="S206" s="2" t="n"/>
+      <c r="T206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>21.02.2026</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+      <c r="J207" s="158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="2" t="n"/>
+      <c r="L207" s="2" t="n"/>
+      <c r="M207" s="2" t="n"/>
+      <c r="N207" s="2" t="n"/>
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
+      <c r="Q207" s="2" t="n"/>
+      <c r="R207" s="2" t="n"/>
+      <c r="S207" s="2" t="n"/>
+      <c r="T207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>3 - 3</t>
+        </is>
+      </c>
+      <c r="J208" s="157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" s="2" t="n"/>
+      <c r="L208" s="2" t="n"/>
+      <c r="M208" s="2" t="n"/>
+      <c r="N208" s="2" t="n"/>
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
+      <c r="Q208" s="2" t="n"/>
+      <c r="R208" s="2" t="n"/>
+      <c r="S208" s="2" t="n"/>
+      <c r="T208" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11868,14 +12033,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64.29%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -11886,14 +12051,14 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77.78%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -11994,14 +12159,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>

--- a/app/placed_bets.xlsx
+++ b/app/placed_bets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -581,6 +581,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -951,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T208"/>
+  <dimension ref="A1:T212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1028,7 +1040,7 @@
         </is>
       </c>
       <c r="K1" s="2" t="n"/>
-      <c r="L1" s="157" t="inlineStr">
+      <c r="L1" s="162" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
@@ -1112,38 +1124,38 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J2" s="157" t="n">
+      <c r="J2" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>55</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73.43000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13210</v>
+        <v>13410</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12270</v>
+        <v>12500</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-940</v>
+        <v>-910</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
         <v>1.31</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1248,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J4" s="157" t="n">
+      <c r="J4" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -1288,7 +1300,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J5" s="157" t="n">
+      <c r="J5" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1340,7 +1352,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J6" s="157" t="n">
+      <c r="J6" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -1444,7 +1456,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J8" s="157" t="n">
+      <c r="J8" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1548,7 +1560,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J10" s="157" t="n">
+      <c r="J10" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1600,7 +1612,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J11" s="157" t="n">
+      <c r="J11" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1704,7 +1716,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J13" s="157" t="n">
+      <c r="J13" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1756,7 +1768,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J14" s="157" t="n">
+      <c r="J14" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1808,7 +1820,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J15" s="157" t="n">
+      <c r="J15" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1860,7 +1872,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J16" s="157" t="n">
+      <c r="J16" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1964,7 +1976,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J18" s="157" t="n">
+      <c r="J18" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -2068,7 +2080,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J20" s="157" t="n">
+      <c r="J20" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -2172,7 +2184,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J22" s="157" t="n">
+      <c r="J22" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -2276,7 +2288,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J24" s="157" t="n">
+      <c r="J24" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -2328,7 +2340,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J25" s="157" t="n">
+      <c r="J25" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -2380,7 +2392,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J26" s="157" t="n">
+      <c r="J26" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2432,7 +2444,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J27" s="157" t="n">
+      <c r="J27" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2484,7 +2496,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J28" s="157" t="n">
+      <c r="J28" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2588,7 +2600,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J30" s="157" t="n">
+      <c r="J30" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2640,7 +2652,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J31" s="157" t="n">
+      <c r="J31" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2692,7 +2704,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J32" s="157" t="n">
+      <c r="J32" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2744,7 +2756,7 @@
           <t>2 - 5</t>
         </is>
       </c>
-      <c r="J33" s="157" t="n">
+      <c r="J33" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2848,7 +2860,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J35" s="157" t="n">
+      <c r="J35" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2900,7 +2912,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J36" s="157" t="n">
+      <c r="J36" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2952,7 +2964,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J37" s="157" t="n">
+      <c r="J37" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3004,7 +3016,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J38" s="157" t="n">
+      <c r="J38" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3056,7 +3068,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J39" s="157" t="n">
+      <c r="J39" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3108,7 +3120,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J40" s="157" t="n">
+      <c r="J40" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3160,7 +3172,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J41" s="157" t="n">
+      <c r="J41" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3212,7 +3224,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J42" s="157" t="n">
+      <c r="J42" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -3316,7 +3328,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J44" s="157" t="n">
+      <c r="J44" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3420,7 +3432,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J46" s="157" t="n">
+      <c r="J46" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -3472,7 +3484,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J47" s="157" t="n">
+      <c r="J47" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3576,7 +3588,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J49" s="157" t="n">
+      <c r="J49" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3628,7 +3640,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J50" s="157" t="n">
+      <c r="J50" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3680,7 +3692,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J51" s="157" t="n">
+      <c r="J51" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3784,7 +3796,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J53" s="157" t="n">
+      <c r="J53" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="2" t="n"/>
@@ -3940,7 +3952,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J56" s="157" t="n">
+      <c r="J56" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -3992,7 +4004,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J57" s="157" t="n">
+      <c r="J57" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4044,7 +4056,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J58" s="157" t="n">
+      <c r="J58" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4252,7 +4264,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J62" s="157" t="n">
+      <c r="J62" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4304,7 +4316,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J63" s="157" t="n">
+      <c r="J63" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4356,7 +4368,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J64" s="157" t="n">
+      <c r="J64" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4408,7 +4420,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J65" s="157" t="n">
+      <c r="J65" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4512,7 +4524,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J67" s="157" t="n">
+      <c r="J67" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -4564,7 +4576,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J68" s="157" t="n">
+      <c r="J68" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4616,7 +4628,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J69" s="157" t="n">
+      <c r="J69" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4668,7 +4680,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J70" s="157" t="n">
+      <c r="J70" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4772,7 +4784,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J72" s="157" t="n">
+      <c r="J72" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -4824,7 +4836,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J73" s="157" t="n">
+      <c r="J73" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -4876,7 +4888,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J74" s="157" t="n">
+      <c r="J74" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -4928,7 +4940,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J75" s="157" t="n">
+      <c r="J75" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -4980,7 +4992,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J76" s="157" t="n">
+      <c r="J76" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5136,7 +5148,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J79" s="157" t="n">
+      <c r="J79" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5240,7 +5252,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J81" s="157" t="n">
+      <c r="J81" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5292,7 +5304,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J82" s="157" t="n">
+      <c r="J82" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5448,7 +5460,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J85" s="157" t="n">
+      <c r="J85" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5500,7 +5512,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J86" s="157" t="n">
+      <c r="J86" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5552,7 +5564,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J87" s="157" t="n">
+      <c r="J87" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5604,7 +5616,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J88" s="157" t="n">
+      <c r="J88" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -5656,7 +5668,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J89" s="157" t="n">
+      <c r="J89" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -5708,7 +5720,7 @@
           <t>1 - 6</t>
         </is>
       </c>
-      <c r="J90" s="157" t="n">
+      <c r="J90" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -5760,7 +5772,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J91" s="157" t="n">
+      <c r="J91" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -5812,7 +5824,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J92" s="157" t="n">
+      <c r="J92" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -5864,7 +5876,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J93" s="157" t="n">
+      <c r="J93" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -5916,7 +5928,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J94" s="157" t="n">
+      <c r="J94" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -5968,7 +5980,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J95" s="157" t="n">
+      <c r="J95" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6020,7 +6032,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J96" s="157" t="n">
+      <c r="J96" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="n"/>
@@ -6072,7 +6084,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J97" s="157" t="n">
+      <c r="J97" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="2" t="n"/>
@@ -6124,7 +6136,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J98" s="157" t="n">
+      <c r="J98" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n"/>
@@ -6228,7 +6240,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J100" s="157" t="n">
+      <c r="J100" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="2" t="n"/>
@@ -6280,7 +6292,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J101" s="157" t="n">
+      <c r="J101" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n"/>
@@ -6332,7 +6344,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J102" s="157" t="n">
+      <c r="J102" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n"/>
@@ -6436,7 +6448,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J104" s="157" t="n">
+      <c r="J104" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n"/>
@@ -6488,7 +6500,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J105" s="157" t="n">
+      <c r="J105" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -6540,7 +6552,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J106" s="157" t="n">
+      <c r="J106" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -6592,7 +6604,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J107" s="157" t="n">
+      <c r="J107" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -6644,7 +6656,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J108" s="157" t="n">
+      <c r="J108" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6748,7 +6760,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J110" s="157" t="n">
+      <c r="J110" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6800,7 +6812,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J111" s="157" t="n">
+      <c r="J111" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6852,7 +6864,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J112" s="157" t="n">
+      <c r="J112" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="2" t="n"/>
@@ -6904,7 +6916,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J113" s="157" t="n">
+      <c r="J113" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n"/>
@@ -6956,7 +6968,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J114" s="157" t="n">
+      <c r="J114" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n"/>
@@ -7008,7 +7020,7 @@
           <t>4 - 3</t>
         </is>
       </c>
-      <c r="J115" s="157" t="n">
+      <c r="J115" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n"/>
@@ -7060,7 +7072,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J116" s="157" t="n">
+      <c r="J116" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -7112,7 +7124,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J117" s="157" t="n">
+      <c r="J117" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7164,7 +7176,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J118" s="157" t="n">
+      <c r="J118" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="2" t="n"/>
@@ -7268,7 +7280,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J120" s="157" t="n">
+      <c r="J120" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -7320,7 +7332,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J121" s="157" t="n">
+      <c r="J121" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="2" t="n"/>
@@ -7424,7 +7436,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J123" s="157" t="n">
+      <c r="J123" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="2" t="n"/>
@@ -7476,7 +7488,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J124" s="157" t="n">
+      <c r="J124" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="2" t="n"/>
@@ -7528,7 +7540,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J125" s="157" t="n">
+      <c r="J125" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="2" t="n"/>
@@ -7632,7 +7644,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J127" s="157" t="n">
+      <c r="J127" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="2" t="n"/>
@@ -7684,7 +7696,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J128" s="157" t="n">
+      <c r="J128" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="2" t="n"/>
@@ -7736,7 +7748,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J129" s="157" t="n">
+      <c r="J129" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="2" t="n"/>
@@ -7840,7 +7852,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J131" s="157" t="n">
+      <c r="J131" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="2" t="n"/>
@@ -7892,7 +7904,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J132" s="157" t="n">
+      <c r="J132" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="2" t="n"/>
@@ -7944,7 +7956,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J133" s="157" t="n">
+      <c r="J133" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="2" t="n"/>
@@ -7996,7 +8008,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J134" s="157" t="n">
+      <c r="J134" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="2" t="n"/>
@@ -8048,7 +8060,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J135" s="157" t="n">
+      <c r="J135" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="2" t="n"/>
@@ -8100,7 +8112,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J136" s="157" t="n">
+      <c r="J136" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="2" t="n"/>
@@ -8152,7 +8164,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J137" s="157" t="n">
+      <c r="J137" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="2" t="n"/>
@@ -8204,7 +8216,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J138" s="157" t="n">
+      <c r="J138" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -8256,7 +8268,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J139" s="157" t="n">
+      <c r="J139" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -8308,7 +8320,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J140" s="157" t="n">
+      <c r="J140" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="2" t="n"/>
@@ -8360,7 +8372,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J141" s="157" t="n">
+      <c r="J141" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="2" t="n"/>
@@ -8412,7 +8424,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J142" s="157" t="n">
+      <c r="J142" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="2" t="n"/>
@@ -8516,7 +8528,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J144" s="157" t="n">
+      <c r="J144" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -8620,7 +8632,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J146" s="157" t="n">
+      <c r="J146" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="2" t="n"/>
@@ -8672,7 +8684,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J147" s="157" t="n">
+      <c r="J147" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="2" t="n"/>
@@ -8724,7 +8736,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J148" s="157" t="n">
+      <c r="J148" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="2" t="n"/>
@@ -8828,7 +8840,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J150" s="157" t="n">
+      <c r="J150" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8880,7 +8892,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J151" s="157" t="n">
+      <c r="J151" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8932,7 +8944,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J152" s="157" t="n">
+      <c r="J152" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -9192,7 +9204,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J157" s="157" t="n">
+      <c r="J157" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n"/>
@@ -9244,7 +9256,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J158" s="157" t="n">
+      <c r="J158" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="2" t="n"/>
@@ -9296,7 +9308,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J159" s="157" t="n">
+      <c r="J159" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="2" t="n"/>
@@ -9348,7 +9360,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J160" s="157" t="n">
+      <c r="J160" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="2" t="n"/>
@@ -9504,7 +9516,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J163" s="157" t="n">
+      <c r="J163" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -9556,7 +9568,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J164" s="157" t="n">
+      <c r="J164" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="2" t="n"/>
@@ -9608,7 +9620,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J165" s="157" t="n">
+      <c r="J165" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="2" t="n"/>
@@ -9712,7 +9724,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J167" s="157" t="n">
+      <c r="J167" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="2" t="n"/>
@@ -9816,7 +9828,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J169" s="157" t="n">
+      <c r="J169" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="2" t="n"/>
@@ -9868,7 +9880,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J170" s="157" t="n">
+      <c r="J170" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="2" t="n"/>
@@ -9920,7 +9932,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J171" s="157" t="n">
+      <c r="J171" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9972,7 +9984,7 @@
           <t>6 - 2</t>
         </is>
       </c>
-      <c r="J172" s="157" t="n">
+      <c r="J172" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="2" t="n"/>
@@ -10024,7 +10036,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J173" s="157" t="n">
+      <c r="J173" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="2" t="n"/>
@@ -10076,7 +10088,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J174" s="157" t="n">
+      <c r="J174" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="2" t="n"/>
@@ -10180,7 +10192,7 @@
           <t>6 - 1</t>
         </is>
       </c>
-      <c r="J176" s="157" t="n">
+      <c r="J176" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -10284,7 +10296,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J178" s="157" t="n">
+      <c r="J178" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="2" t="n"/>
@@ -10336,7 +10348,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J179" s="157" t="n">
+      <c r="J179" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="2" t="n"/>
@@ -10388,7 +10400,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J180" s="157" t="n">
+      <c r="J180" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="2" t="n"/>
@@ -10440,7 +10452,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J181" s="157" t="n">
+      <c r="J181" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n"/>
@@ -10492,7 +10504,7 @@
           <t>6 - 0</t>
         </is>
       </c>
-      <c r="J182" s="157" t="n">
+      <c r="J182" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n"/>
@@ -10596,7 +10608,7 @@
           <t>2 - 4</t>
         </is>
       </c>
-      <c r="J184" s="157" t="n">
+      <c r="J184" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="2" t="n"/>
@@ -10648,7 +10660,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J185" s="157" t="n">
+      <c r="J185" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="2" t="n"/>
@@ -10752,7 +10764,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J187" s="157" t="n">
+      <c r="J187" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="2" t="n"/>
@@ -10856,7 +10868,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J189" s="157" t="n">
+      <c r="J189" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="2" t="n"/>
@@ -10908,7 +10920,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J190" s="157" t="n">
+      <c r="J190" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="2" t="n"/>
@@ -11012,7 +11024,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J192" s="157" t="n">
+      <c r="J192" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="2" t="n"/>
@@ -11064,7 +11076,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J193" s="157" t="n">
+      <c r="J193" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K193" s="2" t="n"/>
@@ -11168,7 +11180,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J195" s="157" t="n">
+      <c r="J195" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K195" s="2" t="n"/>
@@ -11272,7 +11284,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J197" s="157" t="n">
+      <c r="J197" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K197" s="2" t="n"/>
@@ -11324,7 +11336,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J198" s="157" t="n">
+      <c r="J198" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -11376,7 +11388,7 @@
           <t>3 - 5</t>
         </is>
       </c>
-      <c r="J199" s="157" t="n">
+      <c r="J199" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K199" s="2" t="n"/>
@@ -11480,7 +11492,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J201" s="157" t="n">
+      <c r="J201" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K201" s="2" t="n"/>
@@ -11532,7 +11544,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J202" s="157" t="n">
+      <c r="J202" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K202" s="2" t="n"/>
@@ -11584,7 +11596,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J203" s="157" t="n">
+      <c r="J203" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K203" s="2" t="n"/>
@@ -11688,7 +11700,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J205" s="157" t="n">
+      <c r="J205" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K205" s="2" t="n"/>
@@ -11740,7 +11752,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J206" s="157" t="n">
+      <c r="J206" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K206" s="2" t="n"/>
@@ -11844,7 +11856,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J208" s="157" t="n">
+      <c r="J208" s="162" t="n">
         <v>1</v>
       </c>
       <c r="K208" s="2" t="n"/>
@@ -11857,6 +11869,214 @@
       <c r="R208" s="2" t="n"/>
       <c r="S208" s="2" t="n"/>
       <c r="T208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+      <c r="J209" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" s="2" t="n"/>
+      <c r="L209" s="2" t="n"/>
+      <c r="M209" s="2" t="n"/>
+      <c r="N209" s="2" t="n"/>
+      <c r="O209" s="2" t="n"/>
+      <c r="P209" s="2" t="n"/>
+      <c r="Q209" s="2" t="n"/>
+      <c r="R209" s="2" t="n"/>
+      <c r="S209" s="2" t="n"/>
+      <c r="T209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+      <c r="J210" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="2" t="n"/>
+      <c r="L210" s="2" t="n"/>
+      <c r="M210" s="2" t="n"/>
+      <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="n"/>
+      <c r="P210" s="2" t="n"/>
+      <c r="Q210" s="2" t="n"/>
+      <c r="R210" s="2" t="n"/>
+      <c r="S210" s="2" t="n"/>
+      <c r="T210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>01.03.2026</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>6.000000000000007</v>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+      <c r="J211" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="2" t="n"/>
+      <c r="L211" s="2" t="n"/>
+      <c r="M211" s="2" t="n"/>
+      <c r="N211" s="2" t="n"/>
+      <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
+      <c r="Q211" s="2" t="n"/>
+      <c r="R211" s="2" t="n"/>
+      <c r="S211" s="2" t="n"/>
+      <c r="T211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>14.03.2026</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+      <c r="J212" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" s="2" t="n"/>
+      <c r="L212" s="2" t="n"/>
+      <c r="M212" s="2" t="n"/>
+      <c r="N212" s="2" t="n"/>
+      <c r="O212" s="2" t="n"/>
+      <c r="P212" s="2" t="n"/>
+      <c r="Q212" s="2" t="n"/>
+      <c r="R212" s="2" t="n"/>
+      <c r="S212" s="2" t="n"/>
+      <c r="T212" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11961,14 +12181,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>42.86%</t>
         </is>
       </c>
     </row>
@@ -12105,14 +12325,14 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -12159,14 +12379,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -12375,14 +12595,14 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.24%</t>
         </is>
       </c>
     </row>

--- a/app/placed_bets.xlsx
+++ b/app/placed_bets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -581,6 +581,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -963,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T212"/>
+  <dimension ref="A1:T214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1040,7 +1046,7 @@
         </is>
       </c>
       <c r="K1" s="2" t="n"/>
-      <c r="L1" s="162" t="inlineStr">
+      <c r="L1" s="164" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
@@ -1124,38 +1130,38 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J2" s="162" t="n">
+      <c r="J2" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>55</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73.93000000000001</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13410</v>
+        <v>13510</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12500</v>
+        <v>12613.5</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-910</v>
+        <v>-896.5</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
         <v>1.31</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>120</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="3">
@@ -1248,7 +1254,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J4" s="162" t="n">
+      <c r="J4" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -1300,7 +1306,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J5" s="162" t="n">
+      <c r="J5" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1352,7 +1358,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J6" s="162" t="n">
+      <c r="J6" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -1456,7 +1462,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J8" s="162" t="n">
+      <c r="J8" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1560,7 +1566,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J10" s="162" t="n">
+      <c r="J10" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1612,7 +1618,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J11" s="162" t="n">
+      <c r="J11" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1716,7 +1722,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J13" s="162" t="n">
+      <c r="J13" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1768,7 +1774,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J14" s="162" t="n">
+      <c r="J14" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1820,7 +1826,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J15" s="162" t="n">
+      <c r="J15" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1872,7 +1878,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J16" s="162" t="n">
+      <c r="J16" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1976,7 +1982,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J18" s="162" t="n">
+      <c r="J18" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -2080,7 +2086,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J20" s="162" t="n">
+      <c r="J20" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -2184,7 +2190,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J22" s="162" t="n">
+      <c r="J22" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -2288,7 +2294,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J24" s="162" t="n">
+      <c r="J24" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -2340,7 +2346,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J25" s="162" t="n">
+      <c r="J25" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -2392,7 +2398,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J26" s="162" t="n">
+      <c r="J26" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2444,7 +2450,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J27" s="162" t="n">
+      <c r="J27" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2496,7 +2502,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J28" s="162" t="n">
+      <c r="J28" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2600,7 +2606,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J30" s="162" t="n">
+      <c r="J30" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2652,7 +2658,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J31" s="162" t="n">
+      <c r="J31" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2704,7 +2710,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J32" s="162" t="n">
+      <c r="J32" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2756,7 +2762,7 @@
           <t>2 - 5</t>
         </is>
       </c>
-      <c r="J33" s="162" t="n">
+      <c r="J33" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2860,7 +2866,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J35" s="162" t="n">
+      <c r="J35" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2912,7 +2918,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J36" s="162" t="n">
+      <c r="J36" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2964,7 +2970,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J37" s="162" t="n">
+      <c r="J37" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3016,7 +3022,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J38" s="162" t="n">
+      <c r="J38" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3068,7 +3074,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J39" s="162" t="n">
+      <c r="J39" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3120,7 +3126,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J40" s="162" t="n">
+      <c r="J40" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3172,7 +3178,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J41" s="162" t="n">
+      <c r="J41" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3224,7 +3230,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J42" s="162" t="n">
+      <c r="J42" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -3328,7 +3334,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J44" s="162" t="n">
+      <c r="J44" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3432,7 +3438,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J46" s="162" t="n">
+      <c r="J46" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -3484,7 +3490,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J47" s="162" t="n">
+      <c r="J47" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3588,7 +3594,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J49" s="162" t="n">
+      <c r="J49" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3640,7 +3646,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J50" s="162" t="n">
+      <c r="J50" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3692,7 +3698,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J51" s="162" t="n">
+      <c r="J51" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3796,7 +3802,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J53" s="162" t="n">
+      <c r="J53" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="2" t="n"/>
@@ -3952,7 +3958,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J56" s="162" t="n">
+      <c r="J56" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -4004,7 +4010,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J57" s="162" t="n">
+      <c r="J57" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4056,7 +4062,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J58" s="162" t="n">
+      <c r="J58" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4264,7 +4270,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J62" s="162" t="n">
+      <c r="J62" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4316,7 +4322,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J63" s="162" t="n">
+      <c r="J63" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4368,7 +4374,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J64" s="162" t="n">
+      <c r="J64" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4420,7 +4426,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J65" s="162" t="n">
+      <c r="J65" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4524,7 +4530,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J67" s="162" t="n">
+      <c r="J67" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -4576,7 +4582,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J68" s="162" t="n">
+      <c r="J68" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4628,7 +4634,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J69" s="162" t="n">
+      <c r="J69" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4680,7 +4686,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J70" s="162" t="n">
+      <c r="J70" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4784,7 +4790,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J72" s="162" t="n">
+      <c r="J72" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -4836,7 +4842,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J73" s="162" t="n">
+      <c r="J73" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -4888,7 +4894,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J74" s="162" t="n">
+      <c r="J74" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -4940,7 +4946,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J75" s="162" t="n">
+      <c r="J75" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -4992,7 +4998,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J76" s="162" t="n">
+      <c r="J76" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5148,7 +5154,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J79" s="162" t="n">
+      <c r="J79" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5252,7 +5258,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J81" s="162" t="n">
+      <c r="J81" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5304,7 +5310,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J82" s="162" t="n">
+      <c r="J82" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5460,7 +5466,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J85" s="162" t="n">
+      <c r="J85" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5512,7 +5518,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J86" s="162" t="n">
+      <c r="J86" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5564,7 +5570,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J87" s="162" t="n">
+      <c r="J87" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5616,7 +5622,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J88" s="162" t="n">
+      <c r="J88" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -5668,7 +5674,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J89" s="162" t="n">
+      <c r="J89" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -5720,7 +5726,7 @@
           <t>1 - 6</t>
         </is>
       </c>
-      <c r="J90" s="162" t="n">
+      <c r="J90" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -5772,7 +5778,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J91" s="162" t="n">
+      <c r="J91" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -5824,7 +5830,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J92" s="162" t="n">
+      <c r="J92" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -5876,7 +5882,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J93" s="162" t="n">
+      <c r="J93" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -5928,7 +5934,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J94" s="162" t="n">
+      <c r="J94" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -5980,7 +5986,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J95" s="162" t="n">
+      <c r="J95" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6032,7 +6038,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J96" s="162" t="n">
+      <c r="J96" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="n"/>
@@ -6084,7 +6090,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J97" s="162" t="n">
+      <c r="J97" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="2" t="n"/>
@@ -6136,7 +6142,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J98" s="162" t="n">
+      <c r="J98" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n"/>
@@ -6240,7 +6246,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J100" s="162" t="n">
+      <c r="J100" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="2" t="n"/>
@@ -6292,7 +6298,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J101" s="162" t="n">
+      <c r="J101" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n"/>
@@ -6344,7 +6350,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J102" s="162" t="n">
+      <c r="J102" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n"/>
@@ -6448,7 +6454,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J104" s="162" t="n">
+      <c r="J104" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n"/>
@@ -6500,7 +6506,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J105" s="162" t="n">
+      <c r="J105" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -6552,7 +6558,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J106" s="162" t="n">
+      <c r="J106" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -6604,7 +6610,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J107" s="162" t="n">
+      <c r="J107" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -6656,7 +6662,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J108" s="162" t="n">
+      <c r="J108" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6760,7 +6766,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J110" s="162" t="n">
+      <c r="J110" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6812,7 +6818,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J111" s="162" t="n">
+      <c r="J111" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6864,7 +6870,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J112" s="162" t="n">
+      <c r="J112" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="2" t="n"/>
@@ -6916,7 +6922,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J113" s="162" t="n">
+      <c r="J113" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n"/>
@@ -6968,7 +6974,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J114" s="162" t="n">
+      <c r="J114" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n"/>
@@ -7020,7 +7026,7 @@
           <t>4 - 3</t>
         </is>
       </c>
-      <c r="J115" s="162" t="n">
+      <c r="J115" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n"/>
@@ -7072,7 +7078,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J116" s="162" t="n">
+      <c r="J116" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -7124,7 +7130,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J117" s="162" t="n">
+      <c r="J117" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7176,7 +7182,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J118" s="162" t="n">
+      <c r="J118" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="2" t="n"/>
@@ -7280,7 +7286,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J120" s="162" t="n">
+      <c r="J120" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -7332,7 +7338,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J121" s="162" t="n">
+      <c r="J121" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="2" t="n"/>
@@ -7436,7 +7442,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J123" s="162" t="n">
+      <c r="J123" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="2" t="n"/>
@@ -7488,7 +7494,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J124" s="162" t="n">
+      <c r="J124" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="2" t="n"/>
@@ -7540,7 +7546,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J125" s="162" t="n">
+      <c r="J125" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="2" t="n"/>
@@ -7644,7 +7650,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J127" s="162" t="n">
+      <c r="J127" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="2" t="n"/>
@@ -7696,7 +7702,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J128" s="162" t="n">
+      <c r="J128" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="2" t="n"/>
@@ -7748,7 +7754,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J129" s="162" t="n">
+      <c r="J129" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="2" t="n"/>
@@ -7852,7 +7858,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J131" s="162" t="n">
+      <c r="J131" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="2" t="n"/>
@@ -7904,7 +7910,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J132" s="162" t="n">
+      <c r="J132" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="2" t="n"/>
@@ -7956,7 +7962,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J133" s="162" t="n">
+      <c r="J133" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="2" t="n"/>
@@ -8008,7 +8014,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J134" s="162" t="n">
+      <c r="J134" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="2" t="n"/>
@@ -8060,7 +8066,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J135" s="162" t="n">
+      <c r="J135" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="2" t="n"/>
@@ -8112,7 +8118,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J136" s="162" t="n">
+      <c r="J136" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="2" t="n"/>
@@ -8164,7 +8170,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J137" s="162" t="n">
+      <c r="J137" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="2" t="n"/>
@@ -8216,7 +8222,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J138" s="162" t="n">
+      <c r="J138" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -8268,7 +8274,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J139" s="162" t="n">
+      <c r="J139" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -8320,7 +8326,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J140" s="162" t="n">
+      <c r="J140" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="2" t="n"/>
@@ -8372,7 +8378,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J141" s="162" t="n">
+      <c r="J141" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="2" t="n"/>
@@ -8424,7 +8430,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J142" s="162" t="n">
+      <c r="J142" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="2" t="n"/>
@@ -8528,7 +8534,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J144" s="162" t="n">
+      <c r="J144" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -8632,7 +8638,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J146" s="162" t="n">
+      <c r="J146" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="2" t="n"/>
@@ -8684,7 +8690,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J147" s="162" t="n">
+      <c r="J147" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="2" t="n"/>
@@ -8736,7 +8742,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J148" s="162" t="n">
+      <c r="J148" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="2" t="n"/>
@@ -8840,7 +8846,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J150" s="162" t="n">
+      <c r="J150" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8892,7 +8898,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J151" s="162" t="n">
+      <c r="J151" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8944,7 +8950,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J152" s="162" t="n">
+      <c r="J152" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -9204,7 +9210,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J157" s="162" t="n">
+      <c r="J157" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n"/>
@@ -9256,7 +9262,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J158" s="162" t="n">
+      <c r="J158" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="2" t="n"/>
@@ -9308,7 +9314,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J159" s="162" t="n">
+      <c r="J159" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="2" t="n"/>
@@ -9360,7 +9366,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J160" s="162" t="n">
+      <c r="J160" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="2" t="n"/>
@@ -9516,7 +9522,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J163" s="162" t="n">
+      <c r="J163" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -9568,7 +9574,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J164" s="162" t="n">
+      <c r="J164" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="2" t="n"/>
@@ -9620,7 +9626,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J165" s="162" t="n">
+      <c r="J165" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="2" t="n"/>
@@ -9724,7 +9730,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J167" s="162" t="n">
+      <c r="J167" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="2" t="n"/>
@@ -9828,7 +9834,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J169" s="162" t="n">
+      <c r="J169" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="2" t="n"/>
@@ -9880,7 +9886,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J170" s="162" t="n">
+      <c r="J170" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="2" t="n"/>
@@ -9932,7 +9938,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J171" s="162" t="n">
+      <c r="J171" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9984,7 +9990,7 @@
           <t>6 - 2</t>
         </is>
       </c>
-      <c r="J172" s="162" t="n">
+      <c r="J172" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="2" t="n"/>
@@ -10036,7 +10042,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J173" s="162" t="n">
+      <c r="J173" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="2" t="n"/>
@@ -10088,7 +10094,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J174" s="162" t="n">
+      <c r="J174" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="2" t="n"/>
@@ -10192,7 +10198,7 @@
           <t>6 - 1</t>
         </is>
       </c>
-      <c r="J176" s="162" t="n">
+      <c r="J176" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -10296,7 +10302,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J178" s="162" t="n">
+      <c r="J178" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="2" t="n"/>
@@ -10348,7 +10354,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J179" s="162" t="n">
+      <c r="J179" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="2" t="n"/>
@@ -10400,7 +10406,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J180" s="162" t="n">
+      <c r="J180" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="2" t="n"/>
@@ -10452,7 +10458,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J181" s="162" t="n">
+      <c r="J181" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n"/>
@@ -10504,7 +10510,7 @@
           <t>6 - 0</t>
         </is>
       </c>
-      <c r="J182" s="162" t="n">
+      <c r="J182" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n"/>
@@ -10608,7 +10614,7 @@
           <t>2 - 4</t>
         </is>
       </c>
-      <c r="J184" s="162" t="n">
+      <c r="J184" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="2" t="n"/>
@@ -10660,7 +10666,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J185" s="162" t="n">
+      <c r="J185" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="2" t="n"/>
@@ -10764,7 +10770,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J187" s="162" t="n">
+      <c r="J187" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="2" t="n"/>
@@ -10868,7 +10874,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J189" s="162" t="n">
+      <c r="J189" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="2" t="n"/>
@@ -10920,7 +10926,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J190" s="162" t="n">
+      <c r="J190" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="2" t="n"/>
@@ -11024,7 +11030,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J192" s="162" t="n">
+      <c r="J192" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="2" t="n"/>
@@ -11076,7 +11082,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J193" s="162" t="n">
+      <c r="J193" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K193" s="2" t="n"/>
@@ -11180,7 +11186,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J195" s="162" t="n">
+      <c r="J195" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K195" s="2" t="n"/>
@@ -11284,7 +11290,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J197" s="162" t="n">
+      <c r="J197" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K197" s="2" t="n"/>
@@ -11336,7 +11342,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J198" s="162" t="n">
+      <c r="J198" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -11388,7 +11394,7 @@
           <t>3 - 5</t>
         </is>
       </c>
-      <c r="J199" s="162" t="n">
+      <c r="J199" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K199" s="2" t="n"/>
@@ -11492,7 +11498,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J201" s="162" t="n">
+      <c r="J201" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K201" s="2" t="n"/>
@@ -11544,7 +11550,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J202" s="162" t="n">
+      <c r="J202" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K202" s="2" t="n"/>
@@ -11596,7 +11602,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J203" s="162" t="n">
+      <c r="J203" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K203" s="2" t="n"/>
@@ -11700,7 +11706,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J205" s="162" t="n">
+      <c r="J205" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K205" s="2" t="n"/>
@@ -11752,7 +11758,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J206" s="162" t="n">
+      <c r="J206" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K206" s="2" t="n"/>
@@ -11856,7 +11862,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J208" s="162" t="n">
+      <c r="J208" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K208" s="2" t="n"/>
@@ -11908,7 +11914,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J209" s="162" t="n">
+      <c r="J209" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K209" s="2" t="n"/>
@@ -11960,7 +11966,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J210" s="162" t="n">
+      <c r="J210" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K210" s="2" t="n"/>
@@ -12012,7 +12018,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J211" s="162" t="n">
+      <c r="J211" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K211" s="2" t="n"/>
@@ -12064,7 +12070,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J212" s="162" t="n">
+      <c r="J212" s="164" t="n">
         <v>1</v>
       </c>
       <c r="K212" s="2" t="n"/>
@@ -12077,6 +12083,110 @@
       <c r="R212" s="2" t="n"/>
       <c r="S212" s="2" t="n"/>
       <c r="T212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>04.04.2026</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munchen</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>2 - 3</t>
+        </is>
+      </c>
+      <c r="J213" s="164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" s="2" t="n"/>
+      <c r="L213" s="2" t="n"/>
+      <c r="M213" s="2" t="n"/>
+      <c r="N213" s="2" t="n"/>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
+      <c r="Q213" s="2" t="n"/>
+      <c r="R213" s="2" t="n"/>
+      <c r="S213" s="2" t="n"/>
+      <c r="T213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>St.Pauli</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munchen</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>5.000000000000007</v>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>0 - 5</t>
+        </is>
+      </c>
+      <c r="J214" s="164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="2" t="n"/>
+      <c r="L214" s="2" t="n"/>
+      <c r="M214" s="2" t="n"/>
+      <c r="N214" s="2" t="n"/>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="n"/>
+      <c r="Q214" s="2" t="n"/>
+      <c r="R214" s="2" t="n"/>
+      <c r="S214" s="2" t="n"/>
+      <c r="T214" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12289,14 +12399,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>

--- a/app/placed_bets.xlsx
+++ b/app/placed_bets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -602,6 +602,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -969,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T214"/>
+  <dimension ref="A1:T216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1046,7 +1052,7 @@
         </is>
       </c>
       <c r="K1" s="2" t="n"/>
-      <c r="L1" s="164" t="inlineStr">
+      <c r="L1" s="165" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
@@ -1130,38 +1136,38 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J2" s="164" t="n">
+      <c r="J2" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>74.18000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13510</v>
+        <v>13610</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12613.5</v>
+        <v>12672</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-896.5</v>
+        <v>-938</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
         <v>1.31</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>133.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -1254,7 +1260,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J4" s="164" t="n">
+      <c r="J4" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -1306,7 +1312,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J5" s="164" t="n">
+      <c r="J5" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1358,7 +1364,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J6" s="164" t="n">
+      <c r="J6" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -1462,7 +1468,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J8" s="164" t="n">
+      <c r="J8" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1566,7 +1572,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J10" s="164" t="n">
+      <c r="J10" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1618,7 +1624,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J11" s="164" t="n">
+      <c r="J11" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1722,7 +1728,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J13" s="164" t="n">
+      <c r="J13" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1774,7 +1780,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J14" s="164" t="n">
+      <c r="J14" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1826,7 +1832,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J15" s="164" t="n">
+      <c r="J15" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1878,7 +1884,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J16" s="164" t="n">
+      <c r="J16" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1982,7 +1988,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J18" s="164" t="n">
+      <c r="J18" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -2086,7 +2092,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J20" s="164" t="n">
+      <c r="J20" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -2190,7 +2196,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J22" s="164" t="n">
+      <c r="J22" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -2294,7 +2300,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J24" s="164" t="n">
+      <c r="J24" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -2346,7 +2352,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J25" s="164" t="n">
+      <c r="J25" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -2398,7 +2404,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J26" s="164" t="n">
+      <c r="J26" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2450,7 +2456,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J27" s="164" t="n">
+      <c r="J27" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2502,7 +2508,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J28" s="164" t="n">
+      <c r="J28" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2606,7 +2612,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J30" s="164" t="n">
+      <c r="J30" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2658,7 +2664,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J31" s="164" t="n">
+      <c r="J31" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2710,7 +2716,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J32" s="164" t="n">
+      <c r="J32" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2762,7 +2768,7 @@
           <t>2 - 5</t>
         </is>
       </c>
-      <c r="J33" s="164" t="n">
+      <c r="J33" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2866,7 +2872,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J35" s="164" t="n">
+      <c r="J35" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2918,7 +2924,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J36" s="164" t="n">
+      <c r="J36" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2970,7 +2976,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J37" s="164" t="n">
+      <c r="J37" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3022,7 +3028,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J38" s="164" t="n">
+      <c r="J38" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3074,7 +3080,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J39" s="164" t="n">
+      <c r="J39" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3126,7 +3132,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J40" s="164" t="n">
+      <c r="J40" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3178,7 +3184,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J41" s="164" t="n">
+      <c r="J41" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3230,7 +3236,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J42" s="164" t="n">
+      <c r="J42" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -3334,7 +3340,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J44" s="164" t="n">
+      <c r="J44" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3438,7 +3444,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J46" s="164" t="n">
+      <c r="J46" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -3490,7 +3496,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J47" s="164" t="n">
+      <c r="J47" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3594,7 +3600,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J49" s="164" t="n">
+      <c r="J49" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3646,7 +3652,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J50" s="164" t="n">
+      <c r="J50" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3698,7 +3704,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J51" s="164" t="n">
+      <c r="J51" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3802,7 +3808,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J53" s="164" t="n">
+      <c r="J53" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="2" t="n"/>
@@ -3958,7 +3964,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J56" s="164" t="n">
+      <c r="J56" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -4010,7 +4016,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J57" s="164" t="n">
+      <c r="J57" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4062,7 +4068,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J58" s="164" t="n">
+      <c r="J58" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4270,7 +4276,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J62" s="164" t="n">
+      <c r="J62" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4322,7 +4328,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J63" s="164" t="n">
+      <c r="J63" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4374,7 +4380,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J64" s="164" t="n">
+      <c r="J64" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4426,7 +4432,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J65" s="164" t="n">
+      <c r="J65" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4530,7 +4536,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J67" s="164" t="n">
+      <c r="J67" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -4582,7 +4588,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J68" s="164" t="n">
+      <c r="J68" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4634,7 +4640,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J69" s="164" t="n">
+      <c r="J69" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4686,7 +4692,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J70" s="164" t="n">
+      <c r="J70" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4790,7 +4796,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J72" s="164" t="n">
+      <c r="J72" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -4842,7 +4848,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J73" s="164" t="n">
+      <c r="J73" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -4894,7 +4900,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J74" s="164" t="n">
+      <c r="J74" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -4946,7 +4952,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J75" s="164" t="n">
+      <c r="J75" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -4998,7 +5004,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J76" s="164" t="n">
+      <c r="J76" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5154,7 +5160,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J79" s="164" t="n">
+      <c r="J79" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5258,7 +5264,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J81" s="164" t="n">
+      <c r="J81" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5310,7 +5316,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J82" s="164" t="n">
+      <c r="J82" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5466,7 +5472,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J85" s="164" t="n">
+      <c r="J85" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5518,7 +5524,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J86" s="164" t="n">
+      <c r="J86" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5570,7 +5576,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J87" s="164" t="n">
+      <c r="J87" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5622,7 +5628,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J88" s="164" t="n">
+      <c r="J88" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -5674,7 +5680,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J89" s="164" t="n">
+      <c r="J89" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -5726,7 +5732,7 @@
           <t>1 - 6</t>
         </is>
       </c>
-      <c r="J90" s="164" t="n">
+      <c r="J90" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -5778,7 +5784,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J91" s="164" t="n">
+      <c r="J91" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -5830,7 +5836,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J92" s="164" t="n">
+      <c r="J92" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -5882,7 +5888,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J93" s="164" t="n">
+      <c r="J93" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -5934,7 +5940,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J94" s="164" t="n">
+      <c r="J94" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -5986,7 +5992,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J95" s="164" t="n">
+      <c r="J95" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6038,7 +6044,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J96" s="164" t="n">
+      <c r="J96" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="n"/>
@@ -6090,7 +6096,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J97" s="164" t="n">
+      <c r="J97" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="2" t="n"/>
@@ -6142,7 +6148,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J98" s="164" t="n">
+      <c r="J98" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n"/>
@@ -6246,7 +6252,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J100" s="164" t="n">
+      <c r="J100" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="2" t="n"/>
@@ -6298,7 +6304,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J101" s="164" t="n">
+      <c r="J101" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n"/>
@@ -6350,7 +6356,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J102" s="164" t="n">
+      <c r="J102" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n"/>
@@ -6454,7 +6460,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J104" s="164" t="n">
+      <c r="J104" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n"/>
@@ -6506,7 +6512,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J105" s="164" t="n">
+      <c r="J105" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -6558,7 +6564,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J106" s="164" t="n">
+      <c r="J106" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -6610,7 +6616,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J107" s="164" t="n">
+      <c r="J107" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -6662,7 +6668,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J108" s="164" t="n">
+      <c r="J108" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6766,7 +6772,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J110" s="164" t="n">
+      <c r="J110" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6818,7 +6824,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J111" s="164" t="n">
+      <c r="J111" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6870,7 +6876,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J112" s="164" t="n">
+      <c r="J112" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="2" t="n"/>
@@ -6922,7 +6928,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J113" s="164" t="n">
+      <c r="J113" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n"/>
@@ -6974,7 +6980,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J114" s="164" t="n">
+      <c r="J114" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n"/>
@@ -7026,7 +7032,7 @@
           <t>4 - 3</t>
         </is>
       </c>
-      <c r="J115" s="164" t="n">
+      <c r="J115" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n"/>
@@ -7078,7 +7084,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J116" s="164" t="n">
+      <c r="J116" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -7130,7 +7136,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J117" s="164" t="n">
+      <c r="J117" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7182,7 +7188,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J118" s="164" t="n">
+      <c r="J118" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="2" t="n"/>
@@ -7286,7 +7292,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J120" s="164" t="n">
+      <c r="J120" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -7338,7 +7344,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J121" s="164" t="n">
+      <c r="J121" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="2" t="n"/>
@@ -7442,7 +7448,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J123" s="164" t="n">
+      <c r="J123" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="2" t="n"/>
@@ -7494,7 +7500,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J124" s="164" t="n">
+      <c r="J124" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="2" t="n"/>
@@ -7546,7 +7552,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J125" s="164" t="n">
+      <c r="J125" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="2" t="n"/>
@@ -7650,7 +7656,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J127" s="164" t="n">
+      <c r="J127" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="2" t="n"/>
@@ -7702,7 +7708,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J128" s="164" t="n">
+      <c r="J128" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="2" t="n"/>
@@ -7754,7 +7760,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J129" s="164" t="n">
+      <c r="J129" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="2" t="n"/>
@@ -7858,7 +7864,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J131" s="164" t="n">
+      <c r="J131" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="2" t="n"/>
@@ -7910,7 +7916,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J132" s="164" t="n">
+      <c r="J132" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="2" t="n"/>
@@ -7962,7 +7968,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J133" s="164" t="n">
+      <c r="J133" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="2" t="n"/>
@@ -8014,7 +8020,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J134" s="164" t="n">
+      <c r="J134" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="2" t="n"/>
@@ -8066,7 +8072,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J135" s="164" t="n">
+      <c r="J135" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="2" t="n"/>
@@ -8118,7 +8124,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J136" s="164" t="n">
+      <c r="J136" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="2" t="n"/>
@@ -8170,7 +8176,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J137" s="164" t="n">
+      <c r="J137" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="2" t="n"/>
@@ -8222,7 +8228,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J138" s="164" t="n">
+      <c r="J138" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -8274,7 +8280,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J139" s="164" t="n">
+      <c r="J139" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -8326,7 +8332,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J140" s="164" t="n">
+      <c r="J140" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="2" t="n"/>
@@ -8378,7 +8384,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J141" s="164" t="n">
+      <c r="J141" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="2" t="n"/>
@@ -8430,7 +8436,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J142" s="164" t="n">
+      <c r="J142" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="2" t="n"/>
@@ -8534,7 +8540,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J144" s="164" t="n">
+      <c r="J144" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -8638,7 +8644,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J146" s="164" t="n">
+      <c r="J146" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="2" t="n"/>
@@ -8690,7 +8696,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J147" s="164" t="n">
+      <c r="J147" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="2" t="n"/>
@@ -8742,7 +8748,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J148" s="164" t="n">
+      <c r="J148" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="2" t="n"/>
@@ -8846,7 +8852,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J150" s="164" t="n">
+      <c r="J150" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8898,7 +8904,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J151" s="164" t="n">
+      <c r="J151" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8950,7 +8956,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J152" s="164" t="n">
+      <c r="J152" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -9210,7 +9216,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J157" s="164" t="n">
+      <c r="J157" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n"/>
@@ -9262,7 +9268,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J158" s="164" t="n">
+      <c r="J158" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="2" t="n"/>
@@ -9314,7 +9320,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J159" s="164" t="n">
+      <c r="J159" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="2" t="n"/>
@@ -9366,7 +9372,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J160" s="164" t="n">
+      <c r="J160" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="2" t="n"/>
@@ -9522,7 +9528,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J163" s="164" t="n">
+      <c r="J163" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -9574,7 +9580,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J164" s="164" t="n">
+      <c r="J164" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="2" t="n"/>
@@ -9626,7 +9632,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J165" s="164" t="n">
+      <c r="J165" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="2" t="n"/>
@@ -9730,7 +9736,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J167" s="164" t="n">
+      <c r="J167" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="2" t="n"/>
@@ -9834,7 +9840,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J169" s="164" t="n">
+      <c r="J169" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="2" t="n"/>
@@ -9886,7 +9892,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J170" s="164" t="n">
+      <c r="J170" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="2" t="n"/>
@@ -9938,7 +9944,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J171" s="164" t="n">
+      <c r="J171" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9990,7 +9996,7 @@
           <t>6 - 2</t>
         </is>
       </c>
-      <c r="J172" s="164" t="n">
+      <c r="J172" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="2" t="n"/>
@@ -10042,7 +10048,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J173" s="164" t="n">
+      <c r="J173" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="2" t="n"/>
@@ -10094,7 +10100,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J174" s="164" t="n">
+      <c r="J174" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="2" t="n"/>
@@ -10198,7 +10204,7 @@
           <t>6 - 1</t>
         </is>
       </c>
-      <c r="J176" s="164" t="n">
+      <c r="J176" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -10302,7 +10308,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J178" s="164" t="n">
+      <c r="J178" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="2" t="n"/>
@@ -10354,7 +10360,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J179" s="164" t="n">
+      <c r="J179" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="2" t="n"/>
@@ -10406,7 +10412,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J180" s="164" t="n">
+      <c r="J180" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="2" t="n"/>
@@ -10458,7 +10464,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J181" s="164" t="n">
+      <c r="J181" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n"/>
@@ -10510,7 +10516,7 @@
           <t>6 - 0</t>
         </is>
       </c>
-      <c r="J182" s="164" t="n">
+      <c r="J182" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n"/>
@@ -10614,7 +10620,7 @@
           <t>2 - 4</t>
         </is>
       </c>
-      <c r="J184" s="164" t="n">
+      <c r="J184" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="2" t="n"/>
@@ -10666,7 +10672,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J185" s="164" t="n">
+      <c r="J185" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="2" t="n"/>
@@ -10770,7 +10776,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J187" s="164" t="n">
+      <c r="J187" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="2" t="n"/>
@@ -10874,7 +10880,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J189" s="164" t="n">
+      <c r="J189" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="2" t="n"/>
@@ -10926,7 +10932,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J190" s="164" t="n">
+      <c r="J190" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="2" t="n"/>
@@ -11030,7 +11036,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J192" s="164" t="n">
+      <c r="J192" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="2" t="n"/>
@@ -11082,7 +11088,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J193" s="164" t="n">
+      <c r="J193" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K193" s="2" t="n"/>
@@ -11186,7 +11192,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J195" s="164" t="n">
+      <c r="J195" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K195" s="2" t="n"/>
@@ -11290,7 +11296,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J197" s="164" t="n">
+      <c r="J197" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K197" s="2" t="n"/>
@@ -11342,7 +11348,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J198" s="164" t="n">
+      <c r="J198" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -11394,7 +11400,7 @@
           <t>3 - 5</t>
         </is>
       </c>
-      <c r="J199" s="164" t="n">
+      <c r="J199" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K199" s="2" t="n"/>
@@ -11498,7 +11504,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J201" s="164" t="n">
+      <c r="J201" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K201" s="2" t="n"/>
@@ -11550,7 +11556,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J202" s="164" t="n">
+      <c r="J202" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K202" s="2" t="n"/>
@@ -11602,7 +11608,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J203" s="164" t="n">
+      <c r="J203" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K203" s="2" t="n"/>
@@ -11706,7 +11712,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J205" s="164" t="n">
+      <c r="J205" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K205" s="2" t="n"/>
@@ -11758,7 +11764,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J206" s="164" t="n">
+      <c r="J206" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K206" s="2" t="n"/>
@@ -11862,7 +11868,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J208" s="164" t="n">
+      <c r="J208" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K208" s="2" t="n"/>
@@ -11914,7 +11920,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J209" s="164" t="n">
+      <c r="J209" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K209" s="2" t="n"/>
@@ -11966,7 +11972,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J210" s="164" t="n">
+      <c r="J210" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K210" s="2" t="n"/>
@@ -12018,7 +12024,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J211" s="164" t="n">
+      <c r="J211" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K211" s="2" t="n"/>
@@ -12070,7 +12076,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J212" s="164" t="n">
+      <c r="J212" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K212" s="2" t="n"/>
@@ -12122,7 +12128,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J213" s="164" t="n">
+      <c r="J213" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K213" s="2" t="n"/>
@@ -12174,7 +12180,7 @@
           <t>0 - 5</t>
         </is>
       </c>
-      <c r="J214" s="164" t="n">
+      <c r="J214" s="165" t="n">
         <v>1</v>
       </c>
       <c r="K214" s="2" t="n"/>
@@ -12187,6 +12193,110 @@
       <c r="R214" s="2" t="n"/>
       <c r="S214" s="2" t="n"/>
       <c r="T214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Olympique Lyon</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+      <c r="J215" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" s="2" t="n"/>
+      <c r="L215" s="2" t="n"/>
+      <c r="M215" s="2" t="n"/>
+      <c r="N215" s="2" t="n"/>
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="n"/>
+      <c r="Q215" s="2" t="n"/>
+      <c r="R215" s="2" t="n"/>
+      <c r="S215" s="2" t="n"/>
+      <c r="T215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>02.05.2026</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munchen</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>3 - 3</t>
+        </is>
+      </c>
+      <c r="J216" s="158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="2" t="n"/>
+      <c r="L216" s="2" t="n"/>
+      <c r="M216" s="2" t="n"/>
+      <c r="N216" s="2" t="n"/>
+      <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
+      <c r="Q216" s="2" t="n"/>
+      <c r="R216" s="2" t="n"/>
+      <c r="S216" s="2" t="n"/>
+      <c r="T216" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12399,14 +12509,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.82%</t>
         </is>
       </c>
     </row>
@@ -12633,14 +12743,14 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>

--- a/app/placed_bets.xlsx
+++ b/app/placed_bets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -608,6 +608,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -975,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T216"/>
+  <dimension ref="A1:T217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1052,12 +1055,12 @@
         </is>
       </c>
       <c r="K1" s="2" t="n"/>
-      <c r="L1" s="165" t="inlineStr">
+      <c r="L1" s="166" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="M1" s="158" t="inlineStr">
+      <c r="M1" s="167" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
@@ -1136,38 +1139,38 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J2" s="165" t="n">
+      <c r="J2" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>56</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73.95</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13610</v>
+        <v>13660</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12672</v>
+        <v>12742</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-938</v>
+        <v>-918</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
         <v>1.31</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
@@ -1208,7 +1211,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J3" s="158" t="n">
+      <c r="J3" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n"/>
@@ -1260,7 +1263,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J4" s="165" t="n">
+      <c r="J4" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -1312,7 +1315,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J5" s="165" t="n">
+      <c r="J5" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1364,7 +1367,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J6" s="165" t="n">
+      <c r="J6" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -1416,7 +1419,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J7" s="158" t="n">
+      <c r="J7" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -1468,7 +1471,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J8" s="165" t="n">
+      <c r="J8" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1520,7 +1523,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J9" s="158" t="n">
+      <c r="J9" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1572,7 +1575,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J10" s="165" t="n">
+      <c r="J10" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1624,7 +1627,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J11" s="165" t="n">
+      <c r="J11" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1676,7 +1679,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J12" s="158" t="n">
+      <c r="J12" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1728,7 +1731,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J13" s="165" t="n">
+      <c r="J13" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1780,7 +1783,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J14" s="165" t="n">
+      <c r="J14" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1832,7 +1835,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J15" s="165" t="n">
+      <c r="J15" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1884,7 +1887,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J16" s="165" t="n">
+      <c r="J16" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1936,7 +1939,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J17" s="158" t="n">
+      <c r="J17" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -1988,7 +1991,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J18" s="165" t="n">
+      <c r="J18" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -2040,7 +2043,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J19" s="158" t="n">
+      <c r="J19" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n"/>
@@ -2092,7 +2095,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J20" s="165" t="n">
+      <c r="J20" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -2144,7 +2147,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J21" s="158" t="n">
+      <c r="J21" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="2" t="n"/>
@@ -2196,7 +2199,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J22" s="165" t="n">
+      <c r="J22" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -2248,7 +2251,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J23" s="158" t="n">
+      <c r="J23" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n"/>
@@ -2300,7 +2303,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J24" s="165" t="n">
+      <c r="J24" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -2352,7 +2355,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J25" s="165" t="n">
+      <c r="J25" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -2404,7 +2407,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J26" s="165" t="n">
+      <c r="J26" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2456,7 +2459,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J27" s="165" t="n">
+      <c r="J27" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2508,7 +2511,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J28" s="165" t="n">
+      <c r="J28" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2560,7 +2563,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J29" s="158" t="n">
+      <c r="J29" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2612,7 +2615,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J30" s="165" t="n">
+      <c r="J30" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2664,7 +2667,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J31" s="165" t="n">
+      <c r="J31" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2716,7 +2719,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J32" s="165" t="n">
+      <c r="J32" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2768,7 +2771,7 @@
           <t>2 - 5</t>
         </is>
       </c>
-      <c r="J33" s="165" t="n">
+      <c r="J33" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2820,7 +2823,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J34" s="158" t="n">
+      <c r="J34" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="2" t="n"/>
@@ -2872,7 +2875,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J35" s="165" t="n">
+      <c r="J35" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2924,7 +2927,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J36" s="165" t="n">
+      <c r="J36" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2976,7 +2979,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J37" s="165" t="n">
+      <c r="J37" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3028,7 +3031,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J38" s="165" t="n">
+      <c r="J38" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3080,7 +3083,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J39" s="165" t="n">
+      <c r="J39" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3132,7 +3135,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J40" s="165" t="n">
+      <c r="J40" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3184,7 +3187,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J41" s="165" t="n">
+      <c r="J41" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3236,7 +3239,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J42" s="165" t="n">
+      <c r="J42" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -3288,7 +3291,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J43" s="158" t="n">
+      <c r="J43" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="2" t="n"/>
@@ -3340,7 +3343,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J44" s="165" t="n">
+      <c r="J44" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3392,7 +3395,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J45" s="158" t="n">
+      <c r="J45" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="2" t="n"/>
@@ -3444,7 +3447,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J46" s="165" t="n">
+      <c r="J46" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -3496,7 +3499,7 @@
           <t>5 - 1</t>
         </is>
       </c>
-      <c r="J47" s="165" t="n">
+      <c r="J47" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3548,7 +3551,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J48" s="158" t="n">
+      <c r="J48" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n"/>
@@ -3600,7 +3603,7 @@
           <t>7 - 1</t>
         </is>
       </c>
-      <c r="J49" s="165" t="n">
+      <c r="J49" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3652,7 +3655,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J50" s="165" t="n">
+      <c r="J50" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3704,7 +3707,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J51" s="165" t="n">
+      <c r="J51" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3756,7 +3759,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J52" s="158" t="n">
+      <c r="J52" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="2" t="n"/>
@@ -3808,7 +3811,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J53" s="165" t="n">
+      <c r="J53" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="2" t="n"/>
@@ -3860,7 +3863,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J54" s="158" t="n">
+      <c r="J54" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="2" t="n"/>
@@ -3912,7 +3915,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J55" s="158" t="n">
+      <c r="J55" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="2" t="n"/>
@@ -3964,7 +3967,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J56" s="165" t="n">
+      <c r="J56" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -4016,7 +4019,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J57" s="165" t="n">
+      <c r="J57" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4068,7 +4071,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J58" s="165" t="n">
+      <c r="J58" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4120,7 +4123,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J59" s="158" t="n">
+      <c r="J59" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="2" t="n"/>
@@ -4172,7 +4175,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J60" s="158" t="n">
+      <c r="J60" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="2" t="n"/>
@@ -4224,7 +4227,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J61" s="158" t="n">
+      <c r="J61" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="2" t="n"/>
@@ -4276,7 +4279,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J62" s="165" t="n">
+      <c r="J62" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4328,7 +4331,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J63" s="165" t="n">
+      <c r="J63" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4380,7 +4383,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J64" s="165" t="n">
+      <c r="J64" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4432,7 +4435,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J65" s="165" t="n">
+      <c r="J65" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4484,7 +4487,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J66" s="158" t="n">
+      <c r="J66" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="2" t="n"/>
@@ -4536,7 +4539,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J67" s="165" t="n">
+      <c r="J67" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -4588,7 +4591,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J68" s="165" t="n">
+      <c r="J68" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4640,7 +4643,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J69" s="165" t="n">
+      <c r="J69" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4692,7 +4695,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J70" s="165" t="n">
+      <c r="J70" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4744,7 +4747,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J71" s="158" t="n">
+      <c r="J71" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="2" t="n"/>
@@ -4796,7 +4799,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J72" s="165" t="n">
+      <c r="J72" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -4848,7 +4851,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J73" s="165" t="n">
+      <c r="J73" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -4900,7 +4903,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J74" s="165" t="n">
+      <c r="J74" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -4952,7 +4955,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J75" s="165" t="n">
+      <c r="J75" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -5004,7 +5007,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J76" s="165" t="n">
+      <c r="J76" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5056,7 +5059,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J77" s="158" t="n">
+      <c r="J77" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K77" s="2" t="n"/>
@@ -5108,7 +5111,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J78" s="158" t="n">
+      <c r="J78" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n"/>
@@ -5160,7 +5163,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J79" s="165" t="n">
+      <c r="J79" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5212,7 +5215,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J80" s="158" t="n">
+      <c r="J80" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="2" t="n"/>
@@ -5264,7 +5267,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J81" s="165" t="n">
+      <c r="J81" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5316,7 +5319,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J82" s="165" t="n">
+      <c r="J82" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5368,7 +5371,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J83" s="158" t="n">
+      <c r="J83" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K83" s="2" t="n"/>
@@ -5420,7 +5423,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J84" s="158" t="n">
+      <c r="J84" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="2" t="n"/>
@@ -5472,7 +5475,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J85" s="165" t="n">
+      <c r="J85" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5524,7 +5527,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J86" s="165" t="n">
+      <c r="J86" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5576,7 +5579,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J87" s="165" t="n">
+      <c r="J87" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5628,7 +5631,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J88" s="165" t="n">
+      <c r="J88" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -5680,7 +5683,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J89" s="165" t="n">
+      <c r="J89" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -5732,7 +5735,7 @@
           <t>1 - 6</t>
         </is>
       </c>
-      <c r="J90" s="165" t="n">
+      <c r="J90" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -5784,7 +5787,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J91" s="165" t="n">
+      <c r="J91" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -5836,7 +5839,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J92" s="165" t="n">
+      <c r="J92" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -5888,7 +5891,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J93" s="165" t="n">
+      <c r="J93" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -5940,7 +5943,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J94" s="165" t="n">
+      <c r="J94" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -5992,7 +5995,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J95" s="165" t="n">
+      <c r="J95" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6044,7 +6047,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J96" s="165" t="n">
+      <c r="J96" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="n"/>
@@ -6096,7 +6099,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J97" s="165" t="n">
+      <c r="J97" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="2" t="n"/>
@@ -6148,7 +6151,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J98" s="165" t="n">
+      <c r="J98" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n"/>
@@ -6200,7 +6203,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J99" s="158" t="n">
+      <c r="J99" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K99" s="2" t="n"/>
@@ -6252,7 +6255,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J100" s="165" t="n">
+      <c r="J100" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="2" t="n"/>
@@ -6304,7 +6307,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J101" s="165" t="n">
+      <c r="J101" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n"/>
@@ -6356,7 +6359,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J102" s="165" t="n">
+      <c r="J102" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n"/>
@@ -6408,7 +6411,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J103" s="158" t="n">
+      <c r="J103" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="2" t="n"/>
@@ -6460,7 +6463,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J104" s="165" t="n">
+      <c r="J104" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n"/>
@@ -6512,7 +6515,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J105" s="165" t="n">
+      <c r="J105" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -6564,7 +6567,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J106" s="165" t="n">
+      <c r="J106" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -6616,7 +6619,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J107" s="165" t="n">
+      <c r="J107" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -6668,7 +6671,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J108" s="165" t="n">
+      <c r="J108" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6720,7 +6723,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J109" s="158" t="n">
+      <c r="J109" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="2" t="n"/>
@@ -6772,7 +6775,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J110" s="165" t="n">
+      <c r="J110" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6824,7 +6827,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J111" s="165" t="n">
+      <c r="J111" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6876,7 +6879,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J112" s="165" t="n">
+      <c r="J112" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="2" t="n"/>
@@ -6928,7 +6931,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J113" s="165" t="n">
+      <c r="J113" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n"/>
@@ -6980,7 +6983,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J114" s="165" t="n">
+      <c r="J114" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n"/>
@@ -7032,7 +7035,7 @@
           <t>4 - 3</t>
         </is>
       </c>
-      <c r="J115" s="165" t="n">
+      <c r="J115" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n"/>
@@ -7084,7 +7087,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J116" s="165" t="n">
+      <c r="J116" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -7136,7 +7139,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J117" s="165" t="n">
+      <c r="J117" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7188,7 +7191,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J118" s="165" t="n">
+      <c r="J118" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="2" t="n"/>
@@ -7240,7 +7243,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J119" s="158" t="n">
+      <c r="J119" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K119" s="2" t="n"/>
@@ -7292,7 +7295,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J120" s="165" t="n">
+      <c r="J120" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -7344,7 +7347,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J121" s="165" t="n">
+      <c r="J121" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="2" t="n"/>
@@ -7396,7 +7399,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J122" s="158" t="n">
+      <c r="J122" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K122" s="2" t="n"/>
@@ -7448,7 +7451,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J123" s="165" t="n">
+      <c r="J123" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="2" t="n"/>
@@ -7500,7 +7503,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J124" s="165" t="n">
+      <c r="J124" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="2" t="n"/>
@@ -7552,7 +7555,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J125" s="165" t="n">
+      <c r="J125" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="2" t="n"/>
@@ -7604,7 +7607,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J126" s="158" t="n">
+      <c r="J126" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K126" s="2" t="n"/>
@@ -7656,7 +7659,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J127" s="165" t="n">
+      <c r="J127" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="2" t="n"/>
@@ -7708,7 +7711,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J128" s="165" t="n">
+      <c r="J128" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="2" t="n"/>
@@ -7760,7 +7763,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J129" s="165" t="n">
+      <c r="J129" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="2" t="n"/>
@@ -7812,7 +7815,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J130" s="158" t="n">
+      <c r="J130" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K130" s="2" t="n"/>
@@ -7864,7 +7867,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J131" s="165" t="n">
+      <c r="J131" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="2" t="n"/>
@@ -7916,7 +7919,7 @@
           <t>0 - 4</t>
         </is>
       </c>
-      <c r="J132" s="165" t="n">
+      <c r="J132" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="2" t="n"/>
@@ -7968,7 +7971,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J133" s="165" t="n">
+      <c r="J133" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="2" t="n"/>
@@ -8020,7 +8023,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J134" s="165" t="n">
+      <c r="J134" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="2" t="n"/>
@@ -8072,7 +8075,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J135" s="165" t="n">
+      <c r="J135" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="2" t="n"/>
@@ -8124,7 +8127,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J136" s="165" t="n">
+      <c r="J136" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="2" t="n"/>
@@ -8176,7 +8179,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J137" s="165" t="n">
+      <c r="J137" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="2" t="n"/>
@@ -8228,7 +8231,7 @@
           <t>5 - 0</t>
         </is>
       </c>
-      <c r="J138" s="165" t="n">
+      <c r="J138" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -8280,7 +8283,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J139" s="165" t="n">
+      <c r="J139" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -8332,7 +8335,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J140" s="165" t="n">
+      <c r="J140" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="2" t="n"/>
@@ -8384,7 +8387,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J141" s="165" t="n">
+      <c r="J141" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="2" t="n"/>
@@ -8436,7 +8439,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J142" s="165" t="n">
+      <c r="J142" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="2" t="n"/>
@@ -8488,7 +8491,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J143" s="158" t="n">
+      <c r="J143" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K143" s="2" t="n"/>
@@ -8540,7 +8543,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J144" s="165" t="n">
+      <c r="J144" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -8592,7 +8595,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J145" s="158" t="n">
+      <c r="J145" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K145" s="2" t="n"/>
@@ -8644,7 +8647,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J146" s="165" t="n">
+      <c r="J146" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="2" t="n"/>
@@ -8696,7 +8699,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J147" s="165" t="n">
+      <c r="J147" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="2" t="n"/>
@@ -8748,7 +8751,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J148" s="165" t="n">
+      <c r="J148" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="2" t="n"/>
@@ -8800,7 +8803,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J149" s="158" t="n">
+      <c r="J149" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K149" s="2" t="n"/>
@@ -8852,7 +8855,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J150" s="165" t="n">
+      <c r="J150" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8904,7 +8907,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J151" s="165" t="n">
+      <c r="J151" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8956,7 +8959,7 @@
           <t>1 - 4</t>
         </is>
       </c>
-      <c r="J152" s="165" t="n">
+      <c r="J152" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -9008,7 +9011,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J153" s="158" t="n">
+      <c r="J153" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="2" t="n"/>
@@ -9060,7 +9063,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J154" s="158" t="n">
+      <c r="J154" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K154" s="2" t="n"/>
@@ -9112,7 +9115,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J155" s="158" t="n">
+      <c r="J155" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K155" s="2" t="n"/>
@@ -9164,7 +9167,7 @@
           <t>3 - 4</t>
         </is>
       </c>
-      <c r="J156" s="158" t="n">
+      <c r="J156" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K156" s="2" t="n"/>
@@ -9216,7 +9219,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J157" s="165" t="n">
+      <c r="J157" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n"/>
@@ -9268,7 +9271,7 @@
           <t>5 - 2</t>
         </is>
       </c>
-      <c r="J158" s="165" t="n">
+      <c r="J158" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="2" t="n"/>
@@ -9320,7 +9323,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J159" s="165" t="n">
+      <c r="J159" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="2" t="n"/>
@@ -9372,7 +9375,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J160" s="165" t="n">
+      <c r="J160" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="2" t="n"/>
@@ -9424,7 +9427,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J161" s="158" t="n">
+      <c r="J161" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="2" t="n"/>
@@ -9476,7 +9479,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J162" s="158" t="n">
+      <c r="J162" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="2" t="n"/>
@@ -9528,7 +9531,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J163" s="165" t="n">
+      <c r="J163" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -9580,7 +9583,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J164" s="165" t="n">
+      <c r="J164" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="2" t="n"/>
@@ -9632,7 +9635,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J165" s="165" t="n">
+      <c r="J165" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="2" t="n"/>
@@ -9684,7 +9687,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J166" s="158" t="n">
+      <c r="J166" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K166" s="2" t="n"/>
@@ -9736,7 +9739,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J167" s="165" t="n">
+      <c r="J167" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="2" t="n"/>
@@ -9788,7 +9791,7 @@
           <t>4 - 1</t>
         </is>
       </c>
-      <c r="J168" s="158" t="n">
+      <c r="J168" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K168" s="2" t="n"/>
@@ -9840,7 +9843,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J169" s="165" t="n">
+      <c r="J169" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="2" t="n"/>
@@ -9892,7 +9895,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J170" s="165" t="n">
+      <c r="J170" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="2" t="n"/>
@@ -9944,7 +9947,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J171" s="165" t="n">
+      <c r="J171" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9996,7 +9999,7 @@
           <t>6 - 2</t>
         </is>
       </c>
-      <c r="J172" s="165" t="n">
+      <c r="J172" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="2" t="n"/>
@@ -10048,7 +10051,7 @@
           <t>0 - 6</t>
         </is>
       </c>
-      <c r="J173" s="165" t="n">
+      <c r="J173" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="2" t="n"/>
@@ -10100,7 +10103,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J174" s="165" t="n">
+      <c r="J174" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="2" t="n"/>
@@ -10152,7 +10155,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J175" s="158" t="n">
+      <c r="J175" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K175" s="2" t="n"/>
@@ -10204,7 +10207,7 @@
           <t>6 - 1</t>
         </is>
       </c>
-      <c r="J176" s="165" t="n">
+      <c r="J176" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -10256,7 +10259,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J177" s="158" t="n">
+      <c r="J177" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K177" s="2" t="n"/>
@@ -10308,7 +10311,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J178" s="165" t="n">
+      <c r="J178" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="2" t="n"/>
@@ -10360,7 +10363,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J179" s="165" t="n">
+      <c r="J179" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="2" t="n"/>
@@ -10412,7 +10415,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J180" s="165" t="n">
+      <c r="J180" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="2" t="n"/>
@@ -10464,7 +10467,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J181" s="165" t="n">
+      <c r="J181" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n"/>
@@ -10516,7 +10519,7 @@
           <t>6 - 0</t>
         </is>
       </c>
-      <c r="J182" s="165" t="n">
+      <c r="J182" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n"/>
@@ -10568,7 +10571,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J183" s="158" t="n">
+      <c r="J183" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K183" s="2" t="n"/>
@@ -10620,7 +10623,7 @@
           <t>2 - 4</t>
         </is>
       </c>
-      <c r="J184" s="165" t="n">
+      <c r="J184" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="2" t="n"/>
@@ -10672,7 +10675,7 @@
           <t>1 - 3</t>
         </is>
       </c>
-      <c r="J185" s="165" t="n">
+      <c r="J185" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="2" t="n"/>
@@ -10724,7 +10727,7 @@
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="J186" s="158" t="n">
+      <c r="J186" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K186" s="2" t="n"/>
@@ -10776,7 +10779,7 @@
           <t>3 - 0</t>
         </is>
       </c>
-      <c r="J187" s="165" t="n">
+      <c r="J187" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="2" t="n"/>
@@ -10828,7 +10831,7 @@
           <t>0 - 0</t>
         </is>
       </c>
-      <c r="J188" s="158" t="n">
+      <c r="J188" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K188" s="2" t="n"/>
@@ -10880,7 +10883,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J189" s="165" t="n">
+      <c r="J189" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="2" t="n"/>
@@ -10932,7 +10935,7 @@
           <t>4 - 2</t>
         </is>
       </c>
-      <c r="J190" s="165" t="n">
+      <c r="J190" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="2" t="n"/>
@@ -10984,7 +10987,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J191" s="158" t="n">
+      <c r="J191" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K191" s="2" t="n"/>
@@ -11036,7 +11039,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J192" s="165" t="n">
+      <c r="J192" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="2" t="n"/>
@@ -11088,7 +11091,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J193" s="165" t="n">
+      <c r="J193" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K193" s="2" t="n"/>
@@ -11140,7 +11143,7 @@
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J194" s="158" t="n">
+      <c r="J194" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K194" s="2" t="n"/>
@@ -11192,7 +11195,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J195" s="165" t="n">
+      <c r="J195" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K195" s="2" t="n"/>
@@ -11244,7 +11247,7 @@
           <t>3 - 1</t>
         </is>
       </c>
-      <c r="J196" s="158" t="n">
+      <c r="J196" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="2" t="n"/>
@@ -11296,7 +11299,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J197" s="165" t="n">
+      <c r="J197" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K197" s="2" t="n"/>
@@ -11348,7 +11351,7 @@
           <t>1 - 1</t>
         </is>
       </c>
-      <c r="J198" s="165" t="n">
+      <c r="J198" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -11400,7 +11403,7 @@
           <t>3 - 5</t>
         </is>
       </c>
-      <c r="J199" s="165" t="n">
+      <c r="J199" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K199" s="2" t="n"/>
@@ -11452,7 +11455,7 @@
           <t>0 - 2</t>
         </is>
       </c>
-      <c r="J200" s="158" t="n">
+      <c r="J200" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K200" s="2" t="n"/>
@@ -11504,7 +11507,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J201" s="165" t="n">
+      <c r="J201" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K201" s="2" t="n"/>
@@ -11556,7 +11559,7 @@
           <t>2 - 0</t>
         </is>
       </c>
-      <c r="J202" s="165" t="n">
+      <c r="J202" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K202" s="2" t="n"/>
@@ -11608,7 +11611,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J203" s="165" t="n">
+      <c r="J203" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K203" s="2" t="n"/>
@@ -11660,7 +11663,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J204" s="158" t="n">
+      <c r="J204" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K204" s="2" t="n"/>
@@ -11712,7 +11715,7 @@
           <t>1 - 2</t>
         </is>
       </c>
-      <c r="J205" s="165" t="n">
+      <c r="J205" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K205" s="2" t="n"/>
@@ -11764,7 +11767,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J206" s="165" t="n">
+      <c r="J206" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K206" s="2" t="n"/>
@@ -11816,7 +11819,7 @@
           <t>2 - 1</t>
         </is>
       </c>
-      <c r="J207" s="158" t="n">
+      <c r="J207" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K207" s="2" t="n"/>
@@ -11868,7 +11871,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J208" s="165" t="n">
+      <c r="J208" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K208" s="2" t="n"/>
@@ -11920,7 +11923,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J209" s="165" t="n">
+      <c r="J209" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K209" s="2" t="n"/>
@@ -11972,7 +11975,7 @@
           <t>0 - 1</t>
         </is>
       </c>
-      <c r="J210" s="165" t="n">
+      <c r="J210" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K210" s="2" t="n"/>
@@ -12024,7 +12027,7 @@
           <t>4 - 0</t>
         </is>
       </c>
-      <c r="J211" s="165" t="n">
+      <c r="J211" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K211" s="2" t="n"/>
@@ -12076,7 +12079,7 @@
           <t>1 - 0</t>
         </is>
       </c>
-      <c r="J212" s="165" t="n">
+      <c r="J212" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K212" s="2" t="n"/>
@@ -12128,7 +12131,7 @@
           <t>2 - 3</t>
         </is>
       </c>
-      <c r="J213" s="165" t="n">
+      <c r="J213" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K213" s="2" t="n"/>
@@ -12180,7 +12183,7 @@
           <t>0 - 5</t>
         </is>
       </c>
-      <c r="J214" s="165" t="n">
+      <c r="J214" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K214" s="2" t="n"/>
@@ -12232,7 +12235,7 @@
           <t>3 - 2</t>
         </is>
       </c>
-      <c r="J215" s="165" t="n">
+      <c r="J215" s="166" t="n">
         <v>1</v>
       </c>
       <c r="K215" s="2" t="n"/>
@@ -12284,7 +12287,7 @@
           <t>3 - 3</t>
         </is>
       </c>
-      <c r="J216" s="158" t="n">
+      <c r="J216" s="167" t="n">
         <v>0</v>
       </c>
       <c r="K216" s="2" t="n"/>
@@ -12297,6 +12300,58 @@
       <c r="R216" s="2" t="n"/>
       <c r="S216" s="2" t="n"/>
       <c r="T216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>09.05.2026</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>3 - 0</t>
+        </is>
+      </c>
+      <c r="J217" s="166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="2" t="n"/>
+      <c r="L217" s="2" t="n"/>
+      <c r="M217" s="2" t="n"/>
+      <c r="N217" s="2" t="n"/>
+      <c r="O217" s="2" t="n"/>
+      <c r="P217" s="2" t="n"/>
+      <c r="Q217" s="2" t="n"/>
+      <c r="R217" s="2" t="n"/>
+      <c r="S217" s="2" t="n"/>
+      <c r="T217" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12401,14 +12456,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.86%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
